--- a/docs/reports/NVDA.xlsx
+++ b/docs/reports/NVDA.xlsx
@@ -161,10 +161,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3429,34 +3429,34 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>222416.14</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>229088.6242</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>235961.282926</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>243040.12141378</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>250331.3250561934</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>257841.2648078793</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>265576.5027521157</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>273543.7978346791</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>281750.1117697195</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <v>290202.6151228111</v>
+        <v>554435.30715</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>571068.3663645</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>588200.4173554351</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>605846.4298760982</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>624021.8227723811</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>642742.4774555527</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>662024.7517792193</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>681885.4943325958</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>702342.0591625738</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>723412.320937451</v>
       </c>
     </row>
     <row r="6">
@@ -3470,39 +3470,39 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="14">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="14">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="14">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="14">
         <f>J5/I5-1</f>
         <v/>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="14">
         <f>K5/J5-1</f>
         <v/>
       </c>
@@ -3513,34 +3513,34 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="15" t="n">
         <v>0.6038168363141272</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>0.6038168363141272</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>0.6038168363141272</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>0.6038168363141272</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="15" t="n">
         <v>0.6038168363141272</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="15" t="n">
         <v>0.6038168363141272</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="15" t="n">
         <v>0.6038168363141272</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="15" t="n">
         <v>0.6038168363141272</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="J7" s="15" t="n">
         <v>0.6038168363141272</v>
       </c>
-      <c r="K7" s="14" t="n">
+      <c r="K7" s="15" t="n">
         <v>0.6038168363141272</v>
       </c>
     </row>
@@ -3550,43 +3550,43 @@
           <t>EBIT (mn)</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="13">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5*F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5*G7</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <f>H5*H7</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="13">
         <f>I5*I7</f>
         <v/>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="13">
         <f>J5*J7</f>
         <v/>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="13">
         <f>K5*K7</f>
         <v/>
       </c>
@@ -3597,35 +3597,35 @@
           <t>Net income (mn)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="12" t="n">
         <v>309167.25903</v>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>127379.0803</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>131200.452709</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>135136.46629027</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>139190.5602789781</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>143366.2770873475</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>147667.2653999679</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>152097.283361967</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>156660.201862826</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>161360.0079187108</v>
+      <c r="C9" s="13" t="n">
+        <v>317528.4829177191</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>327054.3374052508</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>336865.9675274083</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>346971.9465532305</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>357381.1049498275</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>368102.5380983223</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>379145.614241272</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>390519.9826685101</v>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>402235.5821485654</v>
       </c>
     </row>
     <row r="10">
@@ -3718,43 +3718,43 @@
           <t>FCF margin</t>
         </is>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="14">
         <f>B12/B5</f>
         <v/>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="14">
         <f>C12/C5</f>
         <v/>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="14">
         <f>D12/D5</f>
         <v/>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="14">
         <f>E12/E5</f>
         <v/>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>F12/F5</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <f>G12/G5</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <f>H12/H5</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="14">
         <f>I12/I5</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="14">
         <f>J12/J5</f>
         <v/>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="14">
         <f>K12/K5</f>
         <v/>
       </c>
@@ -3865,7 +3865,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="12" t="n">
         <v>24221</v>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       <c r="A15" s="21" t="n">
         <v>2027</v>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="12" t="n">
         <v>269530.4309492308</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3919,7 +3919,7 @@
         <f>1/(1+$B$8)^1</f>
         <v/>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="13">
         <f>B15*D15</f>
         <v/>
       </c>
@@ -3928,7 +3928,7 @@
       <c r="A16" s="21" t="n">
         <v>2028</v>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="12" t="n">
         <v>278963.9960324538</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
         <f>1/(1+$B$8)^2</f>
         <v/>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <f>B16*D16</f>
         <v/>
       </c>
@@ -3949,7 +3949,7 @@
       <c r="A17" s="21" t="n">
         <v>2029</v>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="12" t="n">
         <v>288727.7358935897</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
         <f>1/(1+$B$8)^3</f>
         <v/>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="13">
         <f>B17*D17</f>
         <v/>
       </c>
@@ -3970,7 +3970,7 @@
       <c r="A18" s="21" t="n">
         <v>2030</v>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B18" s="12" t="n">
         <v>298833.2066498654</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3982,7 +3982,7 @@
         <f>1/(1+$B$8)^4</f>
         <v/>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="13">
         <f>B18*D18</f>
         <v/>
       </c>
@@ -3991,7 +3991,7 @@
       <c r="A19" s="21" t="n">
         <v>2031</v>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="12" t="n">
         <v>309292.3688826106</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
         <f>1/(1+$B$8)^5</f>
         <v/>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="13">
         <f>B19*D19</f>
         <v/>
       </c>
@@ -4012,7 +4012,7 @@
       <c r="A20" s="21" t="n">
         <v>2032</v>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="12" t="n">
         <v>320117.6017935019</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
         <f>1/(1+$B$8)^6</f>
         <v/>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="13">
         <f>B20*D20</f>
         <v/>
       </c>
@@ -4033,7 +4033,7 @@
       <c r="A21" s="21" t="n">
         <v>2033</v>
       </c>
-      <c r="B21" s="15" t="n">
+      <c r="B21" s="12" t="n">
         <v>331321.7178562745</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -4045,7 +4045,7 @@
         <f>1/(1+$B$8)^7</f>
         <v/>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="13">
         <f>B21*D21</f>
         <v/>
       </c>
@@ -4054,7 +4054,7 @@
       <c r="A22" s="21" t="n">
         <v>2034</v>
       </c>
-      <c r="B22" s="15" t="n">
+      <c r="B22" s="12" t="n">
         <v>342917.9779812441</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
         <f>1/(1+$B$8)^8</f>
         <v/>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="13">
         <f>B22*D22</f>
         <v/>
       </c>
@@ -4075,7 +4075,7 @@
       <c r="A23" s="21" t="n">
         <v>2035</v>
       </c>
-      <c r="B23" s="15" t="n">
+      <c r="B23" s="12" t="n">
         <v>354920.1072105876</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
         <f>1/(1+$B$8)^9</f>
         <v/>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="13">
         <f>B23*D23</f>
         <v/>
       </c>
@@ -4096,7 +4096,7 @@
       <c r="A24" s="21" t="n">
         <v>2036</v>
       </c>
-      <c r="B24" s="15" t="n">
+      <c r="B24" s="12" t="n">
         <v>367342.3109629581</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
         <f>1/(1+$B$8)^10</f>
         <v/>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="13">
         <f>B24*D24</f>
         <v/>
       </c>
@@ -4137,7 +4137,7 @@
           <t>Terminal value = CFn·(1+g)/(Ke−g)</t>
         </is>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="13">
         <f>B24*(1+$B$10)/($B$8-$B$10)</f>
         <v/>
       </c>
@@ -4148,7 +4148,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="13">
         <f>$B$28/(1+$B$8)^10</f>
         <v/>
       </c>
@@ -4191,7 +4191,7 @@
           <t>Upside / (downside)</t>
         </is>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="14">
         <f>B32/$B$33-1</f>
         <v/>
       </c>
@@ -4260,7 +4260,7 @@
           <t>Diluted shares (mn)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="12" t="n">
         <v>24221</v>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
           <t>Total debt (USDmm)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="12" t="n">
         <v>11040</v>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
           <t>Cash &amp; ST investments (USDmm)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="12" t="n">
         <v>62556</v>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
           <t>Minority interest (USDmm)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
           <t>Net debt (USDmm)</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="13">
         <f>Assumptions!$B$7-Assumptions!$B$8</f>
         <v/>
       </c>
@@ -4378,7 +4378,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
+      <c r="B19" s="15" t="n">
         <v>0.1346049038575892</v>
       </c>
     </row>
@@ -4444,19 +4444,19 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
+      <c r="B26" s="15" t="n">
         <v>0.25</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="15" t="n">
         <v>0.19375</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="15" t="n">
         <v>0.1375</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E26" s="15" t="n">
         <v>0.08124999999999999</v>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="F26" s="15" t="n">
         <v>0.02499999999999999</v>
       </c>
     </row>
@@ -4466,19 +4466,19 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
+      <c r="B27" s="15" t="n">
         <v>0.6038168363141272</v>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="15" t="n">
         <v>0.5928342375578994</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="15" t="n">
         <v>0.5818516388016716</v>
       </c>
-      <c r="E27" s="14" t="n">
+      <c r="E27" s="15" t="n">
         <v>0.5708690400454437</v>
       </c>
-      <c r="F27" s="14" t="n">
+      <c r="F27" s="15" t="n">
         <v>0.5598864412892159</v>
       </c>
     </row>
@@ -4488,19 +4488,19 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
+      <c r="B28" s="15" t="n">
         <v>0.0273514662325203</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="15" t="n">
         <v>0.0273514662325203</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="15" t="n">
         <v>0.0273514662325203</v>
       </c>
-      <c r="E28" s="14" t="n">
+      <c r="E28" s="15" t="n">
         <v>0.0273514662325203</v>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="F28" s="15" t="n">
         <v>0.0273514662325203</v>
       </c>
     </row>
@@ -4510,19 +4510,19 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="15" t="n">
         <v>0.03456977806240261</v>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="15" t="n">
         <v>0.03456977806240261</v>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="15" t="n">
         <v>0.03456977806240261</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="15" t="n">
         <v>0.03456977806240261</v>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="F29" s="15" t="n">
         <v>0.03456977806240261</v>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
           <t>ΔNWC % of Δrevenue</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="15" t="n">
         <v>0.1437222510315231</v>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
           <t>Weight of equity</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <f>WACC!$B$6/(WACC!$B$6+WACC!$B$7)</f>
         <v/>
       </c>
@@ -4629,7 +4629,7 @@
           <t>Weight of debt</t>
         </is>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="14">
         <f>1-WACC!$B$8</f>
         <v/>
       </c>
@@ -4755,23 +4755,23 @@
       <c r="E5" s="29" t="n">
         <v>215938</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="13">
         <f>E5*(1+Assumptions!B$26)</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="13">
         <f>F5*(1+Assumptions!C$26)</f>
         <v/>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="13">
         <f>G5*(1+Assumptions!D$26)</f>
         <v/>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="13">
         <f>H5*(1+Assumptions!E$26)</f>
         <v/>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="13">
         <f>I5*(1+Assumptions!F$26)</f>
         <v/>
       </c>
@@ -4794,23 +4794,23 @@
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="14">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="14">
         <f>J5/I5-1</f>
         <v/>
       </c>
@@ -4833,23 +4833,23 @@
       <c r="E7" s="29" t="n">
         <v>130387</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <f>F5*Assumptions!B$27</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <f>G5*Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="13">
         <f>H5*Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="13">
         <f>I5*Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="13">
         <f>J5*Assumptions!F$27</f>
         <v/>
       </c>
@@ -4876,23 +4876,23 @@
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="14">
         <f>I7/I5</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="14">
         <f>J7/J5</f>
         <v/>
       </c>
@@ -4915,23 +4915,23 @@
       <c r="E9" s="29" t="n">
         <v>2843</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <f>F5*Assumptions!B$28</f>
         <v/>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="13">
         <f>G5*Assumptions!C$28</f>
         <v/>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="13">
         <f>H5*Assumptions!D$28</f>
         <v/>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="13">
         <f>I5*Assumptions!E$28</f>
         <v/>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="13">
         <f>J5*Assumptions!F$28</f>
         <v/>
       </c>
@@ -4958,23 +4958,23 @@
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="13">
         <f>I7+I9</f>
         <v/>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="13">
         <f>J7+J9</f>
         <v/>
       </c>
@@ -5040,23 +5040,23 @@
       <c r="E12" s="29" t="n">
         <v>6042</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="13">
         <f>F5*Assumptions!B$29</f>
         <v/>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="13">
         <f>G5*Assumptions!C$29</f>
         <v/>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="13">
         <f>H5*Assumptions!D$29</f>
         <v/>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="13">
         <f>I5*Assumptions!E$29</f>
         <v/>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="13">
         <f>J5*Assumptions!F$29</f>
         <v/>
       </c>
@@ -5079,23 +5079,23 @@
       <c r="E13" s="29" t="n">
         <v>15949</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>(F5-E5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <f>(G5-F5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <f>(H5-G5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <f>(I5-H5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="13">
         <f>(J5-I5)*Assumptions!$B$30</f>
         <v/>
       </c>
@@ -5294,23 +5294,23 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="13">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5*F7</f>
         <v/>
       </c>
@@ -5321,7 +5321,7 @@
           <t>PV of explicit FCFF</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="13">
         <f>SUM(B8:F8)</f>
         <v/>
       </c>
@@ -5343,7 +5343,7 @@
           <t>Invested capital (mm)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="12" t="n">
         <v>105777</v>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="14">
         <f>MAX($B$11/$B$13,WACC!$B$10)</f>
         <v/>
       </c>
@@ -5386,7 +5386,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="13">
         <f>$B$11*(1+Assumptions!$B$22)*(1-$B$15)/(WACC!$B$10-Assumptions!$B$22)</f>
         <v/>
       </c>
@@ -5397,7 +5397,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="13">
         <f>$B$16/(1+WACC!$B$10)^(5-0.5)</f>
         <v/>
       </c>
@@ -5408,7 +5408,7 @@
           <t>TV as % of EV</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="14">
         <f>$B$17/($B$10+$B$17)</f>
         <v/>
       </c>
@@ -5521,19 +5521,19 @@
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="15" t="n">
         <v>0.015</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="15" t="n">
         <v>0.02</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="15" t="n">
         <v>0.025</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="15" t="n">
         <v>0.03</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="15" t="n">
         <v>0.035</v>
       </c>
     </row>
